--- a/sheets/민요/검수/옹헤야.xlsx
+++ b/sheets/민요/검수/옹헤야.xlsx
@@ -6505,28 +6505,28 @@
   <sheetFormatPr defaultColWidth="8.0625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="11.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="5.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
@@ -6548,7 +6548,7 @@
       <c r="R2" s="10"/>
       <c r="S2" s="10"/>
     </row>
-    <row r="3" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
       <c r="D3" s="11"/>
@@ -6576,7 +6576,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11"/>
       <c r="C4" s="13"/>
       <c r="D4" s="11"/>
@@ -6604,7 +6604,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11"/>
       <c r="C5" s="13"/>
       <c r="D5" s="11"/>
@@ -6632,7 +6632,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11"/>
       <c r="C6" s="14"/>
       <c r="D6" s="15"/>
@@ -6660,7 +6660,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="11"/>
       <c r="C7" s="12"/>
       <c r="D7" s="11"/>
@@ -6688,7 +6688,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="11"/>
       <c r="C8" s="13"/>
       <c r="D8" s="11"/>
@@ -6716,7 +6716,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="11"/>
       <c r="C9" s="13"/>
       <c r="D9" s="11"/>
@@ -6744,7 +6744,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="11"/>
       <c r="C10" s="14"/>
       <c r="D10" s="11"/>
@@ -6772,7 +6772,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
       <c r="D11" s="11"/>
@@ -6800,7 +6800,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="11"/>
       <c r="C12" s="13"/>
       <c r="D12" s="11"/>
@@ -6828,7 +6828,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="11"/>
       <c r="C13" s="13"/>
       <c r="D13" s="11"/>
@@ -6856,7 +6856,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="11"/>
       <c r="C14" s="14"/>
       <c r="D14" s="11"/>
@@ -6884,7 +6884,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="11"/>
       <c r="C15" s="12"/>
       <c r="D15" s="11"/>
@@ -6908,7 +6908,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="11"/>
       <c r="C16" s="13"/>
       <c r="D16" s="11"/>
@@ -6932,7 +6932,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="11"/>
       <c r="C17" s="13"/>
       <c r="D17" s="11"/>
@@ -6956,7 +6956,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="15"/>
       <c r="C18" s="16"/>
       <c r="D18" s="15"/>

--- a/sheets/민요/검수/옹헤야.xlsx
+++ b/sheets/민요/검수/옹헤야.xlsx
@@ -44,7 +44,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">파일</t>
@@ -63,7 +63,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">민요</t>
@@ -80,7 +80,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">옹헤야</t>
@@ -115,7 +115,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박자 </t>
@@ -134,7 +134,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">행수</t>
@@ -153,7 +153,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -173,7 +173,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">비고</t>
@@ -192,7 +192,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">노란 칸</t>
@@ -216,7 +216,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">팔레트 외 글자</t>
@@ -235,7 +235,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">주황 칸</t>
@@ -267,7 +267,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">비고 </t>
@@ -284,7 +284,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박자 근사</t>
@@ -301,7 +301,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">한 장에 두 곡</t>
@@ -317,7 +317,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">민요채보</t>
@@ -334,7 +334,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">군밤타령 옹헤야</t>
@@ -353,7 +353,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">손격자 </t>
@@ -370,7 +370,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -387,7 +387,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">굵은 선 </t>
@@ -404,7 +404,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">칸마다 → </t>
@@ -421,7 +421,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간마다 칸이 있음</t>
@@ -438,7 +438,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">한 장에 두 곡</t>
@@ -455,7 +455,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">상단 띠는 제목행</t>
@@ -472,7 +472,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">왼쪽 </t>
@@ -489,7 +489,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">옹헤야</t>
@@ -506,7 +506,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">자진모리</t>
@@ -523,7 +523,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">오른쪽 </t>
@@ -540,7 +540,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">군밤타령</t>
@@ -557,7 +557,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">으로 정간 아님</t>
@@ -574,7 +574,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명 줄 </t>
@@ -591,7 +591,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">개</t>
@@ -608,7 +608,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">오른쪽부터</t>
@@ -625,7 +625,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -642,7 +642,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">은 비어 있음</t>
@@ -659,7 +659,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -676,7 +676,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">는 정간</t>
@@ -693,7 +693,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">지운 글자와 가사 </t>
@@ -710,7 +710,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">에</t>
@@ -727,7 +727,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -744,7 +744,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">에 율명이 있고 그 위로 세로선 한 줄이 그어져 있음</t>
@@ -761,7 +761,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">지운 것인지 불명</t>
@@ -778,7 +778,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">보이는 대로 적음</t>
@@ -795,7 +795,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -812,7 +812,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">군밤타령</t>
@@ -829,7 +829,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">바람이 분다 … 돈바람 분다 </t>
@@ -846,7 +846,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">얼싸 좋네 하 좋아 군밤이요 에헤라 생율 밤이로구나</t>
@@ -863,7 +863,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -880,7 +880,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -897,7 +897,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">는 세로줄 여러 개로 지워져 비움</t>
@@ -914,7 +914,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -931,7 +931,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">에 </t>
@@ -948,7 +948,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">두번</t>
@@ -965,7 +965,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">메모</t>
@@ -982,7 +982,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -999,7 +999,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -1016,7 +1016,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">을 감싼 네모와 연결</t>
@@ -1033,7 +1033,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -1050,7 +1050,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">옹헤야</t>
@@ -1067,7 +1067,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -1084,7 +1084,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">메기는 소리 </t>
@@ -1101,7 +1101,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">에헤 에헤 옹해야 어절씨구 옹해야 잘도 한다 옹해야</t>
@@ -1118,7 +1118,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -1135,7 +1135,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">받는 소리 </t>
@@ -1152,7 +1152,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">옹헤야 옹헤야 모두 같이 옹헤야 즐거웁게 옹헤야 노래하세 옹헤야</t>
@@ -1169,7 +1169,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">女변이 없는 古 모양</t>
@@ -1186,7 +1186,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">十이 口 안으로 내려옴</t>
@@ -1203,7 +1203,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">은 南 흘림으로</t>
@@ -1220,7 +1220,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">女변이 분명한 것만 姑로 판독</t>
@@ -1237,7 +1237,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">黃</t>
@@ -1254,7 +1254,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢은 같은 가락에서도 氵 유무가 섞여 있어 보이는 대로 적음</t>
@@ -1271,7 +1271,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">동그라미 친 黃은 氵 없음</t>
@@ -1288,7 +1288,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">가사 칸의 </t>
@@ -1305,7 +1305,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">표시</t>
@@ -1322,7 +1322,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">옹 앞 등</t>
@@ -1339,7 +1339,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">는 기호표 위치가 아니라 생략</t>
@@ -1356,7 +1356,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">하단 </t>
@@ -1373,7 +1373,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박</t>
@@ -1390,7 +1390,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">메모와 양식번호 </t>
@@ -1407,7 +1407,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">은 곡과 무관</t>
@@ -1432,7 +1432,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">원본처럼 오른쪽이 </t>
@@ -1449,7 +1449,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄</t>
@@ -1466,7 +1466,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">악보 시트도 같은 배치</t>
@@ -1483,7 +1483,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">여러 페이지는 악보 시트 아래쪽으로 이어짐</t>
@@ -1500,7 +1500,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">빈 행 </t>
@@ -1517,7 +1517,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">개</t>
@@ -1534,7 +1534,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">인쇄 시 페이지마다 새 종이</t>
@@ -1551,7 +1551,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄은 항상 맨 오른쪽 두 열</t>
@@ -1568,7 +1568,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명</t>
@@ -1585,7 +1585,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">가사</t>
@@ -1602,7 +1602,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박자는 </t>
@@ -1619,7 +1619,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -1636,7 +1636,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박자는 </t>
@@ -1653,7 +1653,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간마다 가사 칸 가로선을 묶음</t>
@@ -1670,7 +1670,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명 글자는 가사의 두 배</t>
@@ -1687,7 +1687,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">인쇄는 </t>
@@ -1704,7 +1704,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">세로</t>
@@ -1721,7 +1721,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">원본 한 페이지 </t>
@@ -1738,7 +1738,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">종이 한 장</t>
@@ -1755,7 +1755,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간 번호 열</t>
@@ -1772,7 +1772,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">머리 행 없음 — 제목 행 아래 </t>
@@ -1789,7 +1789,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">번째 행이 정간 </t>
@@ -1806,7 +1806,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">이므로 행을 지우거나 끼워 넣지 말고</t>
@@ -1823,7 +1823,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">제목 병합도 풀지 말 것</t>
@@ -1840,7 +1840,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">한 장이 </t>
@@ -1857,7 +1857,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄을 넘으면 </t>
@@ -1874,7 +1874,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">줄씩 다음 페이지</t>
@@ -1887,7 +1887,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간 안에서 위→아래 순서</t>
@@ -1904,7 +1904,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">칸 안 줄바꿈으로 구분 </t>
@@ -1921,7 +1921,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">앱과 같음</t>
@@ -1943,7 +1943,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">– 연음 </t>
@@ -1960,7 +1960,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">쉼 </t>
@@ -1977,7 +1977,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">점 </t>
@@ -1994,7 +1994,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">동그라미 </t>
@@ -2011,7 +2011,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">두 점 </t>
@@ -2028,7 +2028,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간 경계 표시 </t>
@@ -2045,7 +2045,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">／ 사선 </t>
@@ -2062,7 +2062,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">／ 는 화면 표시 전용</t>
@@ -2090,7 +2090,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명</t>
@@ -2107,7 +2107,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">기호표에 없는 글자 </t>
@@ -2124,7 +2124,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">포함</t>
@@ -2141,7 +2141,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">반드시 수정</t>
@@ -2154,7 +2154,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">악보 시트를 고쳐 </t>
@@ -2171,7 +2171,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">로 저장한 뒤 </t>
@@ -2188,7 +2188,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">작업</t>
@@ -2205,7 +2205,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">실행 → </t>
@@ -2222,7 +2222,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">반영</t>
@@ -2239,7 +2239,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정보</t>
@@ -2256,7 +2256,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간목록 시트는 반영 안 됨</t>
@@ -2279,7 +2279,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명</t>
@@ -2298,7 +2298,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">판독</t>
@@ -2319,7 +2319,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">율명</t>
@@ -2338,7 +2338,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">앱</t>
@@ -2370,7 +2370,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">지운 글자</t>
@@ -2387,7 +2387,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">동그라미</t>
@@ -2404,7 +2404,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">가새표</t>
@@ -2421,7 +2421,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">비움</t>
@@ -2434,7 +2434,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2451,7 +2451,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2465,7 +2465,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">정간</t>
@@ -2482,7 +2482,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">위로 세로선 한 줄 그어짐</t>
@@ -2501,7 +2501,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2521,7 +2521,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2540,7 +2540,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2557,7 +2557,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -2574,7 +2574,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2592,7 +2592,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -2609,7 +2609,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2623,7 +2623,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2640,7 +2640,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2660,7 +2660,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2677,7 +2677,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2695,7 +2695,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -2712,7 +2712,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -2746,7 +2746,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -2763,7 +2763,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -2778,7 +2778,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">黃</t>
@@ -2795,7 +2795,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -2813,7 +2813,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">첫 黃 동그라미 침</t>
@@ -2830,7 +2830,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">氵 없음</t>
@@ -2849,7 +2849,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2866,7 +2866,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無</t>
@@ -2883,7 +2883,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2901,7 +2901,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -2918,7 +2918,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">姑 흘림</t>
@@ -2935,7 +2935,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">女변 없어 南</t>
@@ -2951,7 +2951,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -2968,7 +2968,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">黃</t>
@@ -2985,7 +2985,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">끝 黃 동그라미 침</t>
@@ -3002,7 +3002,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">氵 없음</t>
@@ -3021,7 +3021,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">姑</t>
@@ -3038,7 +3038,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3052,7 +3052,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3069,7 +3069,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3087,7 +3087,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
@@ -3104,7 +3104,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3121,7 +3121,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3139,7 +3139,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3156,7 +3156,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3174,7 +3174,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3191,7 +3191,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">黃</t>
@@ -3209,7 +3209,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">黃 동그라미 침</t>
@@ -3226,7 +3226,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">氵 없음</t>
@@ -3245,7 +3245,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3262,7 +3262,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3279,7 +3279,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3297,7 +3297,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3323,7 +3323,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3340,7 +3340,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3357,7 +3357,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3384,7 +3384,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3401,7 +3401,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">黃</t>
@@ -3418,7 +3418,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">姑</t>
@@ -3435,7 +3435,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3452,7 +3452,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">汰</t>
@@ -3469,7 +3469,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3495,7 +3495,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3512,7 +3512,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3532,7 +3532,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3549,7 +3549,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3563,7 +3563,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">왼쪽에 </t>
@@ -3580,7 +3580,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">박</t>
@@ -3597,7 +3597,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">메모</t>
@@ -3607,7 +3607,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3624,7 +3624,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3642,7 +3642,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3659,7 +3659,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">南</t>
@@ -3686,7 +3686,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">潢</t>
@@ -3703,7 +3703,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">林</t>
@@ -3780,31 +3780,31 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
@@ -3823,17 +3823,22 @@
     <font>
       <b val="true"/>
       <sz val="24"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="24"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -3927,7 +3932,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4001,6 +4006,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6505,478 +6554,478 @@
   <sheetFormatPr defaultColWidth="8.0625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="20" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="19" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="20" width="5.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
     </row>
     <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="11" t="s">
+      <c r="B3" s="22"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="R3" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="S3" s="23" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="11"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="11" t="s">
+      <c r="B4" s="22"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="Q4" s="13" t="s">
+      <c r="Q4" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="R4" s="11" t="s">
+      <c r="R4" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="S4" s="24" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="11"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="11" t="s">
+      <c r="B5" s="22"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="Q5" s="13" t="s">
+      <c r="Q5" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="R5" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="S5" s="24" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="11" t="s">
+      <c r="B6" s="22"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="Q6" s="14" t="s">
+      <c r="Q6" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="R6" s="15" t="s">
+      <c r="R6" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="S6" s="16" t="s">
+      <c r="S6" s="27" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="11" t="s">
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="Q7" s="12" t="s">
+      <c r="Q7" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="R7" s="11" t="s">
+      <c r="R7" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="S7" s="12" t="s">
+      <c r="S7" s="23" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="11"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="11" t="s">
+      <c r="B8" s="22"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="Q8" s="13" t="s">
+      <c r="Q8" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="R8" s="11" t="s">
+      <c r="R8" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="S8" s="13" t="s">
+      <c r="S8" s="24" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="11" t="s">
+      <c r="B9" s="22"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="Q9" s="13" t="s">
+      <c r="Q9" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="R9" s="11" t="s">
+      <c r="R9" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="S9" s="13" t="s">
+      <c r="S9" s="24" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="11" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="Q10" s="14" t="s">
+      <c r="Q10" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="R10" s="11" t="s">
+      <c r="R10" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="S10" s="14" t="s">
+      <c r="S10" s="25" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="11" t="s">
+      <c r="B11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="Q11" s="12" t="s">
+      <c r="Q11" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="R11" s="11" t="s">
+      <c r="R11" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="S11" s="12" t="s">
+      <c r="S11" s="23" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="11" t="s">
+      <c r="B12" s="22"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="Q12" s="13" t="s">
+      <c r="Q12" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="R12" s="11" t="s">
+      <c r="R12" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="S12" s="13" t="s">
+      <c r="S12" s="24" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="11" t="s">
+      <c r="B13" s="22"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="Q13" s="13" t="s">
+      <c r="Q13" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="R13" s="11" t="s">
+      <c r="R13" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="S13" s="13" t="s">
+      <c r="S13" s="24" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="11" t="s">
+      <c r="B14" s="22"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="Q14" s="14" t="s">
+      <c r="Q14" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="R14" s="11" t="s">
+      <c r="R14" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="S14" s="14" t="s">
+      <c r="S14" s="25" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="11" t="s">
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="S15" s="12" t="s">
+      <c r="S15" s="23" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="11" t="s">
+      <c r="B16" s="22"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="S16" s="13" t="s">
+      <c r="S16" s="24" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="11" t="s">
+      <c r="B17" s="22"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="S17" s="13" t="s">
+      <c r="S17" s="24" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="15"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="15" t="s">
+      <c r="B18" s="26"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="S18" s="16" t="s">
+      <c r="S18" s="27" t="s">
         <v>154</v>
       </c>
     </row>

--- a/sheets/민요/검수/옹헤야.xlsx
+++ b/sheets/민요/검수/옹헤야.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/옹헤야.xlsx
+++ b/sheets/민요/검수/옹헤야.xlsx
@@ -1748,6 +1748,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1756,10 +1759,10 @@
     <col min="5" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="77.61" customHeight="1">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1770,7 +1773,7 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="77.61" customHeight="1">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1796,7 +1799,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="77.61" customHeight="1">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -1824,7 +1827,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="77.61" customHeight="1">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1847,7 +1850,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="77.61" customHeight="1">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -1875,7 +1878,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="77.61" customHeight="1">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -1903,7 +1906,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="77.61" customHeight="1">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -1931,7 +1934,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="77.61" customHeight="1">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -1954,7 +1957,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="77.61" customHeight="1">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -1982,7 +1985,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="77.61" customHeight="1">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2010,7 +2013,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="77.61" customHeight="1">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2038,7 +2041,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="77.61" customHeight="1">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2061,7 +2064,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="77.61" customHeight="1">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2089,7 +2092,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="77.61" customHeight="1">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -2106,7 +2109,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="77.61" customHeight="1">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -2123,7 +2126,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="77.61" customHeight="1">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -2138,7 +2141,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="77.61" customHeight="1">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="25" t="inlineStr">
         <is>
@@ -2165,6 +2168,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/옹헤야.xlsx
+++ b/sheets/민요/검수/옹헤야.xlsx
@@ -1753,9 +1753,9 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
